--- a/doc/事件配置表.xlsx
+++ b/doc/事件配置表.xlsx
@@ -512,7 +512,9 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[主线] 你站在阵法外，浓郁的灵气让你浑身舒泰。突然！你怀中那灰扑扑小物件疯狂发热，贪婪吸收灵气！石皮剥落，光芒大作！</t>
+          <t>[主线] 你站在阵法外，浓郁的灵气让你浑身舒泰。突然！你怀中那灰扑扑小物件疯狂发热，贪婪吸收灵气！石皮剥落，光芒大作！
+【获得：{handName}】{handDescription}
+[系统] 第一卷：凡人俗世 —— 完。你的寿元大限更新为120岁。</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -523,6 +525,102 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>flag:awakenedHand:1;flag:chapterFinished:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>E_0001_Opening</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>[主线] 你揉了揉发胀的脑袋醒来。今年你已经16岁了，作为青石村的普通农家子弟，你一生的轨迹似乎一眼就能望到头。</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>E_6001_Rumor2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[传闻] 猎户张大叔神色慌张：“后山深处最近总有野兽惨叫，还有怪异红光，千万别往深处走！”</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>E_6001_Rumor3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>[传闻] 王婶压低嗓音：“昨夜后山起雾时，我看见有人提着灯往坟地里去，像不是活人。”</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
     </row>
